--- a/04_Figures/F01/c_data/F01_supplementary.xlsx
+++ b/04_Figures/F01/c_data/F01_supplementary.xlsx
@@ -6,25 +6,672 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="panel_A" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="panel_B" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="panel_C" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="SUPP_panel_A" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="SUPP_panel_B" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="SUPP_panel_C" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Table_1A_characteristics" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Table_1B_pre_post" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Table_1C_composition" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Per_participant" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Notes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="panel_A_train_volume" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="panel_B_dxa_lbm" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="panel_C_vl_thickness" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="supp_deadlift_1rm" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="supp_type_II_fcsa" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="supp_type_I_fcsa" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="supp_dxa_fat_mass" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="supp_fat_to_lean" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="263">
+  <si>
+    <t xml:space="preserve">Variable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Young (n=17)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Old (n=15)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age (y)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9 ± 2.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.5 ± 6.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;0.001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Body mass (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.6 ± 13.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.3 ± 10.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMI (kg/m²)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5 ± 2.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7 ± 2.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Training volume, 12 wk (×10⁵ kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2 ± 0.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1 ± 0.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Young Pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Young Post</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Old Pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Old Post</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p Age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p Age x Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DXA lean body mass (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 / 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.6 ± 5.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.3 ± 6.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.3 ± 6.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.5 ± 7.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DXA fat mass (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4 ± 9.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1 ± 9.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2 ± 6.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0 ± 6.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fat-to-lean mass ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34 ± 0.15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33 ± 0.14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52 ± 0.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.51 ± 0.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VL thickness (cm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08 ± 0.60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57 ± 0.47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95 ± 0.41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15 ± 0.40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type I fCSA (µm²)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 / 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4510 ± 1110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5084 ± 1250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5378 ± 1476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4655 ± 1457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type II fCSA (µm²)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5422 ± 1609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6560 ± 1659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4541 ± 1330</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4160 ± 944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deadlift 1RM (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 / 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.3 ± 22.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.9 ± 27.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.8 ± 31.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.3 ± 26.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parent trial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supplement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EAA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Essential amino acids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Placebo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whey protein</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPS_younger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peanut protein</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Old</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beetroot juice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPS_older</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Participant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age_group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parent_trial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parent_ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Body_mass_kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Training_volume_kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DXA_LBM_kg_Pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DXA_LBM_kg_Post</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DXA_LBM_kg_Delta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DXA_FM_kg_Pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DXA_FM_kg_Post</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DXA_FM_kg_Delta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FM_to_LBM_Pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FM_to_LBM_Post</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FM_to_LBM_Delta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VL_thick_cm_Pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VL_thick_cm_Post</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VL_thick_cm_Delta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type_I_fCSA_Pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type_I_fCSA_Post</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type_I_fCSA_Delta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type_II_fCSA_Pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type_II_fCSA_Post</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type_II_fCSA_Delta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deadlift_1rm_kg_Pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deadlift_1rm_kg_Post</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deadlift_1rm_kg_Delta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YP_S14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPS_YS14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YP_S45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPS_YS45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YP_S56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPS_YS56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y_S01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EAA 01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y_S05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EAA 05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y_S07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EAA 07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y_S10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EAA 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y_S11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EAA 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y_S16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EAA 16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y_S28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EAA 28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y_S30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EAA 30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y_S31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EAA 31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y_S32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EAA 32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y_S34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EAA 34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y_S35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EAA 35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y_S36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EAA 36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y_S40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EAA 40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OP_S06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPS006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OP_S11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPS011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OP_S12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPS012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OP_S17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPS017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O_S05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O_S06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O_S07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O_S10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O_S16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O_S17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O_S24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O_S28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O_S29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O_S32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O_S35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cohort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 younger and 15 older men. All participants are male, so sex is not tabulated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Twelve weeks of supervised full-body resistance training, twice weekly, measured before (Pre) and after (Post).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variables measured once per participant. Young against Old by Welch two-sample t-test.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 1B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variables measured at both timepoints. Group x Timepoint mixed ANOVA on participants with a complete pair; n is given per variable as Young / Old.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 1C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parent trial and supplement arm making up each age group. No supplement arm spans both age groups, so no test is reported.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean +/- SD throughout.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fat-to-lean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DXA fat mass divided by DXA lean body mass. Used in place of percent body fat because the NORE trial recorded body mass only at baseline, so a percent-of-weight measure after training would rest on a derived denominator for 11 of the 32 participants.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Missing data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fibre cross-sectional areas and deadlift 1RM are incomplete in the parent trials. The per-variable n in Table 1B counts participants with both timepoints.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Participant ids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Participant is the proteomics sample label. Parent_ID is the participant number inside the parent trial workbook, at 00_input/parent_meta/&lt;Parent_trial&gt;.xlsx.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00_input/YvO_meta.xlsx, via 04_Figures/F01/a_script/04_phenotype_table.R.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abbreviations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DXA, dual-energy x-ray absorptiometry; LBM, lean body mass; VL, vastus lateralis; fCSA, fibre cross-sectional area; 1RM, one-repetition maximum; BMI, body mass index.</t>
+  </si>
   <si>
     <t xml:space="preserve">Group</t>
   </si>
   <si>
-    <t xml:space="preserve">n</t>
-  </si>
-  <si>
     <t xml:space="preserve">mean</t>
   </si>
   <si>
@@ -40,12 +687,6 @@
     <t xml:space="preserve">t_test_p</t>
   </si>
   <si>
-    <t xml:space="preserve">Old</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Young</t>
-  </si>
-  <si>
     <t xml:space="preserve">test</t>
   </si>
   <si>
@@ -77,6 +718,102 @@
   </si>
   <si>
     <t xml:space="preserve">Young vs Old</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2 Table — participants and training outcomes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 1 as printed, the per-participant values behind it, and the source data for Figure 1 and S2 Figure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table_1A_characteristics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 1 upper block: baseline characteristics by age group.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table_1B_pre_post</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 1 lower block: every pre-post measure, with age, time and age-by-time p-values.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table_1C_composition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How many participants each parent trial and supplement arm contributed, by age group.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per_participant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One row per participant: every phenotype value behind Table 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What each measure is, how it was obtained, and which participants are missing it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">panel_A_train_volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figure 1A: training volume per participant and group.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">panel_B_dxa_lbm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figure 1B: DXA lean body mass pre and post, and the change.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">panel_C_vl_thickness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figure 1C: vastus lateralis thickness pre and post, and the change.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">supp_deadlift_1rm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2 Figure A: deadlift one-repetition maximum.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">supp_type_II_fcsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2 Figure B: type II fibre cross-sectional area.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">supp_type_I_fcsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2 Figure C: type I fibre cross-sectional area.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">supp_dxa_fat_mass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2 Figure D: whole-body DXA fat mass.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">supp_fat_to_lean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2 Figure E: fat-to-lean mass ratio.</t>
   </si>
 </sst>
 </file>
@@ -412,82 +1149,216 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="3.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="11.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="11.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="11.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="11.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="105.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="4.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="7.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="85.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>237</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>239</v>
+      </c>
+      <c r="B6" t="n">
         <v>7</v>
       </c>
-      <c r="B2" t="n">
-        <v>15</v>
-      </c>
-      <c r="C2" t="n">
-        <v>211904.046228677</v>
-      </c>
-      <c r="D2" t="n">
-        <v>63961.6607283764</v>
-      </c>
-      <c r="E2" t="n">
-        <v>16514.8297864514</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.988399773207149</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.770720835814133</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="n">
-        <v>17</v>
-      </c>
-      <c r="C3" t="n">
-        <v>217658.101764706</v>
-      </c>
-      <c r="D3" t="n">
-        <v>42922.5057447456</v>
-      </c>
-      <c r="E3" t="n">
-        <v>10410.2367589275</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.505766491328304</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.770720835814133</v>
+      <c r="C6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>241</v>
+      </c>
+      <c r="B7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>243</v>
+      </c>
+      <c r="B8" t="n">
+        <v>32</v>
+      </c>
+      <c r="C8" t="n">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>245</v>
+      </c>
+      <c r="B9" t="n">
+        <v>11</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>247</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>249</v>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>251</v>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>253</v>
+      </c>
+      <c r="B13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>255</v>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>257</v>
+      </c>
+      <c r="B15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" t="n">
+        <v>10</v>
+      </c>
+      <c r="D15" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>259</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D16" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>261</v>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" t="n">
+        <v>10</v>
+      </c>
+      <c r="D17" t="s">
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -496,7 +1367,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -515,127 +1386,127 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>220</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>10</v>
+        <v>221</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>11</v>
+        <v>222</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>223</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>13</v>
+        <v>224</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>14</v>
+        <v>225</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>15</v>
+        <v>226</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>5</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>227</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="C2" t="n">
         <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>3.18997773779259</v>
+        <v>14.7688449703674</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00569641165229446</v>
+        <v>0.000000000096424143015509</v>
       </c>
       <c r="F2" t="n">
         <v>16</v>
       </c>
       <c r="G2" t="n">
-        <v>2.20941176470588</v>
+        <v>34.6428952706309</v>
       </c>
       <c r="H2" t="n">
-        <v>0.741143302304994</v>
+        <v>29.6702885832476</v>
       </c>
       <c r="I2" t="n">
-        <v>3.67768022710677</v>
+        <v>39.6155019580143</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0589546260567265</v>
+        <v>0.644086480755532</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>228</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>91</v>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5719266262061</v>
+        <v>1.86240360275308</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0004351155884287</v>
+        <v>0.0995623583328714</v>
       </c>
       <c r="F3" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G3" t="n">
-        <v>1.18017345392857</v>
+        <v>12.5040445367758</v>
       </c>
       <c r="H3" t="n">
-        <v>0.62652932960883</v>
+        <v>-2.97830223594194</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7338175782483</v>
+        <v>27.9863913094935</v>
       </c>
       <c r="J3" t="n">
-        <v>0.308889212998157</v>
+        <v>0.229218907771102</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>229</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>230</v>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>1.39246199094184</v>
+        <v>3.1129336199642</v>
       </c>
       <c r="E4" t="n">
-        <v>0.178844473519128</v>
+        <v>0.0110084857796522</v>
       </c>
       <c r="F4" t="n">
-        <v>20.3058830697667</v>
+        <v>9.99771301289196</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.02923831077732</v>
+        <v>22.1388507338552</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.511114019968263</v>
+        <v>6.29207433475795</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5695906415229</v>
+        <v>37.9856271329524</v>
       </c>
       <c r="J4"/>
     </row>
@@ -645,7 +1516,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -664,127 +1535,127 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>220</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>10</v>
+        <v>221</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>11</v>
+        <v>222</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>223</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>13</v>
+        <v>224</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>14</v>
+        <v>225</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>15</v>
+        <v>226</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>5</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>227</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>6.55900186025861</v>
+        <v>3.66931242829301</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00000657814233487256</v>
+        <v>0.00321100368707975</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G2" t="n">
-        <v>0.46764705882353</v>
+        <v>1137.81620940155</v>
       </c>
       <c r="H2" t="n">
-        <v>0.316500969938879</v>
+        <v>462.188662471534</v>
       </c>
       <c r="I2" t="n">
-        <v>0.61879314770818</v>
+        <v>1813.44375633157</v>
       </c>
       <c r="J2" t="n">
-        <v>0.154019706948298</v>
+        <v>0.613794637740126</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>228</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>91</v>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.27132264595624</v>
+        <v>-1.12717233951929</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00011816977551927</v>
+        <v>0.288823381952292</v>
       </c>
       <c r="F3" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>0.204666666666667</v>
+        <v>-381.6</v>
       </c>
       <c r="H3" t="n">
-        <v>0.121392245499539</v>
+        <v>-1147.44488729731</v>
       </c>
       <c r="I3" t="n">
-        <v>0.287941087833794</v>
+        <v>384.244887297309</v>
       </c>
       <c r="J3" t="n">
-        <v>0.628876363010418</v>
+        <v>0.166727557880152</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>229</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>230</v>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>3.23928168359076</v>
+        <v>3.30958194824081</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00343861635736173</v>
+        <v>0.00351257266774994</v>
       </c>
       <c r="F4" t="n">
-        <v>24.4402387953263</v>
+        <v>19.9202285945501</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.262980392156863</v>
+        <v>1519.41620940155</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0955828026178479</v>
+        <v>561.512588395082</v>
       </c>
       <c r="I4" t="n">
-        <v>0.430377981695878</v>
+        <v>2477.31983040802</v>
       </c>
       <c r="J4"/>
     </row>
@@ -794,7 +1665,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -813,127 +1684,127 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>220</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>10</v>
+        <v>221</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>11</v>
+        <v>222</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>223</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>13</v>
+        <v>224</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>14</v>
+        <v>225</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>15</v>
+        <v>226</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>5</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>227</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>14.7688449703674</v>
+        <v>2.49285601448109</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0000000000964241430155066</v>
+        <v>0.0282835941098158</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G2" t="n">
-        <v>34.6428952706309</v>
+        <v>574.467097037032</v>
       </c>
       <c r="H2" t="n">
-        <v>29.6702885832475</v>
+        <v>72.3697941944063</v>
       </c>
       <c r="I2" t="n">
-        <v>39.6155019580143</v>
+        <v>1076.56439987966</v>
       </c>
       <c r="J2" t="n">
-        <v>0.644086480755537</v>
+        <v>0.170312055738409</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>228</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>91</v>
       </c>
       <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.75727569644542</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.112745012158823</v>
+      </c>
+      <c r="F3" t="n">
         <v>9</v>
       </c>
-      <c r="D3" t="n">
-        <v>1.87694637635175</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.097361685383249</v>
-      </c>
-      <c r="F3" t="n">
-        <v>8</v>
-      </c>
       <c r="G3" t="n">
-        <v>12.5042713332305</v>
+        <v>-722.6</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.85839526473125</v>
+        <v>-1652.80962455947</v>
       </c>
       <c r="I3" t="n">
-        <v>27.8669379311923</v>
+        <v>207.609624559473</v>
       </c>
       <c r="J3" t="n">
-        <v>0.237257638742384</v>
+        <v>0.485336464164219</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>229</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>230</v>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>3.13448667481087</v>
+        <v>2.75166734950937</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0105726137329648</v>
+        <v>0.015222697911012</v>
       </c>
       <c r="F4" t="n">
-        <v>10.0294265576391</v>
+        <v>14.4704177796216</v>
       </c>
       <c r="G4" t="n">
-        <v>-22.1386239374004</v>
+        <v>1297.06709703703</v>
       </c>
       <c r="H4" t="n">
-        <v>6.40771726946544</v>
+        <v>289.143084851715</v>
       </c>
       <c r="I4" t="n">
-        <v>37.8695306053354</v>
+        <v>2304.99110922235</v>
       </c>
       <c r="J4"/>
     </row>
@@ -943,7 +1814,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -962,127 +1833,127 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>220</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>10</v>
+        <v>221</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>11</v>
+        <v>222</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>223</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>13</v>
+        <v>224</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>14</v>
+        <v>225</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>15</v>
+        <v>226</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>5</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.35735363383874</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.193507827633823</v>
+      </c>
+      <c r="F2" t="n">
         <v>16</v>
       </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="n">
-        <v>13</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2.79441278568396</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.0162113506588155</v>
-      </c>
-      <c r="F2" t="n">
-        <v>12</v>
-      </c>
       <c r="G2" t="n">
-        <v>856.603728058635</v>
+        <v>0.681182352941176</v>
       </c>
       <c r="H2" t="n">
-        <v>188.706987034343</v>
+        <v>-0.382683425096411</v>
       </c>
       <c r="I2" t="n">
-        <v>1524.50046908293</v>
+        <v>1.74504813097876</v>
       </c>
       <c r="J2" t="n">
-        <v>0.629844097930084</v>
+        <v>0.21422736233571</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>228</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>91</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.12717233951929</v>
+        <v>-0.633469012493946</v>
       </c>
       <c r="E3" t="n">
-        <v>0.288823381952292</v>
+        <v>0.536639530994366</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G3" t="n">
-        <v>-381.6</v>
+        <v>-0.252813333333333</v>
       </c>
       <c r="H3" t="n">
-        <v>-1147.44488729731</v>
+        <v>-1.10878365100793</v>
       </c>
       <c r="I3" t="n">
-        <v>384.244887297309</v>
+        <v>0.603156984341269</v>
       </c>
       <c r="J3" t="n">
-        <v>0.166727557880152</v>
+        <v>0.0585899700689724</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>229</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>230</v>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D4" t="n">
-        <v>2.71115529634061</v>
+        <v>1.45665930397974</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0135165137442106</v>
+        <v>0.15585821327628</v>
       </c>
       <c r="F4" t="n">
-        <v>19.8168408558481</v>
+        <v>29.2615544748063</v>
       </c>
       <c r="G4" t="n">
-        <v>-1238.20372805863</v>
+        <v>0.933995686274509</v>
       </c>
       <c r="H4" t="n">
-        <v>284.96473107296</v>
+        <v>-0.376876570956552</v>
       </c>
       <c r="I4" t="n">
-        <v>2191.44272504431</v>
+        <v>2.24486794350557</v>
       </c>
       <c r="J4"/>
     </row>
@@ -1092,7 +1963,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -1111,127 +1982,4158 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>220</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>10</v>
+        <v>221</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>11</v>
+        <v>222</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>223</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>13</v>
+        <v>224</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>14</v>
+        <v>225</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>15</v>
+        <v>226</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>5</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.963225226188543</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.349767551177234</v>
+      </c>
+      <c r="F2" t="n">
         <v>16</v>
       </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="n">
-        <v>13</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2.47802908436044</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.0290628558366825</v>
-      </c>
-      <c r="F2" t="n">
-        <v>12</v>
-      </c>
       <c r="G2" t="n">
-        <v>572.085261566636</v>
+        <v>-0.00833019973133979</v>
       </c>
       <c r="H2" t="n">
-        <v>69.0779661996328</v>
+        <v>-0.0266636424962431</v>
       </c>
       <c r="I2" t="n">
-        <v>1075.09255693364</v>
+        <v>0.0100032430335635</v>
       </c>
       <c r="J2" t="n">
-        <v>0.158997959578344</v>
+        <v>0.867640747635303</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>228</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>91</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.75727569644542</v>
+        <v>-1.768375498774</v>
       </c>
       <c r="E3" t="n">
-        <v>0.112745012158823</v>
+        <v>0.098772493619647</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G3" t="n">
-        <v>-722.6</v>
+        <v>-0.0135681629009314</v>
       </c>
       <c r="H3" t="n">
-        <v>-1652.80962455947</v>
+        <v>-0.0300244049092566</v>
       </c>
       <c r="I3" t="n">
-        <v>207.609624559473</v>
+        <v>0.00288807910739385</v>
       </c>
       <c r="J3" t="n">
-        <v>0.485336464164219</v>
+        <v>0.212688434984506</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C4" t="n">
+        <v>32</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.45306307492892</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.653772223260457</v>
+      </c>
+      <c r="F4" t="n">
+        <v>29.9173119362528</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.00523796316959158</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.0183759406300431</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0288518669692263</v>
+      </c>
+      <c r="J4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="35.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="12.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="9.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
         <v>18</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="23.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="7.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="13.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="13.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="12.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="13.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="9.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="9.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="12.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>43</v>
+      </c>
       <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G6" t="s">
+        <v>63</v>
+      </c>
+      <c r="H6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F7" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H7" t="s">
+        <v>71</v>
+      </c>
+      <c r="I7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F8" t="s">
+        <v>78</v>
+      </c>
+      <c r="G8" t="s">
+        <v>79</v>
+      </c>
+      <c r="H8" t="s">
+        <v>7</v>
+      </c>
+      <c r="I8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="9.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="12.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="21.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="3.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="11.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="9.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="9.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="21.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="3.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="3.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="12.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="11.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="18.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="14.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="15.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="16.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="13.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="14.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="15.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="13.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="14.71" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="15.71" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="15.71" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="16.71" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="17.71" hidden="0" customWidth="1"/>
+    <col min="23" max="23" width="15.71" hidden="0" customWidth="1"/>
+    <col min="24" max="24" width="16.71" hidden="0" customWidth="1"/>
+    <col min="25" max="25" width="17.71" hidden="0" customWidth="1"/>
+    <col min="26" max="26" width="16.71" hidden="0" customWidth="1"/>
+    <col min="27" max="27" width="17.71" hidden="0" customWidth="1"/>
+    <col min="28" max="28" width="18.71" hidden="0" customWidth="1"/>
+    <col min="29" max="29" width="19.71" hidden="0" customWidth="1"/>
+    <col min="30" max="30" width="20.71" hidden="0" customWidth="1"/>
+    <col min="31" max="31" width="21.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G2" t="n">
+        <v>19</v>
+      </c>
+      <c r="H2" t="n">
+        <v>102.8131</v>
+      </c>
+      <c r="I2" t="n">
+        <v>27.5901268706077</v>
+      </c>
+      <c r="J2" t="n">
+        <v>243874.77</v>
+      </c>
+      <c r="K2" t="n">
+        <v>59.39</v>
+      </c>
+      <c r="L2" t="n">
+        <v>67.65</v>
+      </c>
+      <c r="M2" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="N2" t="n">
+        <v>33.98</v>
+      </c>
+      <c r="O2" t="n">
+        <v>35.6727</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.6927</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.572150193635292</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.527312638580931</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-0.0448375550543608</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
+      <c r="AB2"/>
+      <c r="AC2" t="n">
+        <v>102.087114337568</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>148.820326678766</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>46.7332123411979</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G3" t="n">
+        <v>24</v>
+      </c>
+      <c r="H3" t="n">
+        <v>75.7713</v>
+      </c>
+      <c r="I3" t="n">
+        <v>24.3146397040726</v>
+      </c>
+      <c r="J3" t="n">
+        <v>145642.01</v>
+      </c>
+      <c r="K3" t="n">
+        <v>47.01</v>
+      </c>
+      <c r="L3" t="n">
+        <v>50.09</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.08000000000001</v>
+      </c>
+      <c r="N3" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="O3" t="n">
+        <v>21.9289</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-2.1211</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.511593278025952</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.437789978039529</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-0.0738032999864232</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W3"/>
+      <c r="X3"/>
+      <c r="Y3"/>
+      <c r="Z3"/>
+      <c r="AA3"/>
+      <c r="AB3"/>
+      <c r="AC3" t="n">
+        <v>59.8911070780399</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>73.049001814882</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>13.1578947368421</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G4" t="n">
+        <v>19</v>
+      </c>
+      <c r="H4" t="n">
+        <v>94.8276</v>
+      </c>
+      <c r="I4" t="n">
+        <v>27.5817325176947</v>
+      </c>
+      <c r="J4" t="n">
+        <v>233346.19</v>
+      </c>
+      <c r="K4" t="n">
+        <v>65.08</v>
+      </c>
+      <c r="L4" t="n">
+        <v>67.9</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.82000000000001</v>
+      </c>
+      <c r="N4" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="O4" t="n">
+        <v>26.1585</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.4085</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.395666871542717</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.385250368188512</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-0.0104165033542042</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="W4"/>
+      <c r="X4"/>
+      <c r="Y4"/>
+      <c r="Z4"/>
+      <c r="AA4"/>
+      <c r="AB4"/>
+      <c r="AC4" t="n">
+        <v>114.791288566243</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>143.375680580762</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>28.584392014519</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F5" t="s">
+        <v>127</v>
+      </c>
+      <c r="G5" t="n">
+        <v>26</v>
+      </c>
+      <c r="H5" t="n">
+        <v>110.07</v>
+      </c>
+      <c r="I5" t="n">
+        <v>31.142485285882</v>
+      </c>
+      <c r="J5" t="n">
+        <v>231992.18</v>
+      </c>
+      <c r="K5" t="n">
+        <v>64.4</v>
+      </c>
+      <c r="L5" t="n">
+        <v>68.1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.69999999999999</v>
+      </c>
+      <c r="N5" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="O5" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="P5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.635093167701863</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.682819383259912</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.0477262155580487</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="W5" t="n">
+        <v>5406.36696954386</v>
+      </c>
+      <c r="X5" t="n">
+        <v>7351.54732721951</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1945.18035767565</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>6734.20541706667</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>9722.03541358139</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2987.82999651473</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>88.475499092559</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>117.059891107078</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>28.584392014519</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F6" t="s">
+        <v>127</v>
+      </c>
+      <c r="G6" t="n">
+        <v>24</v>
+      </c>
+      <c r="H6" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>21.885128141423</v>
+      </c>
+      <c r="J6" t="n">
+        <v>204730.02</v>
+      </c>
+      <c r="K6" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N6" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="O6" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.799999999999999</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.231968810916179</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.231329690346084</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.000639120570095575</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3199.0951149589</v>
+      </c>
+      <c r="X6" t="n">
+        <v>5529.73088206452</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2330.63576710561</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3048.4416738543</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>5866.6746885</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2818.2330146457</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>90.2903811252268</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>134.301270417423</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>44.0108892921961</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>136</v>
+      </c>
+      <c r="B7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" t="s">
+        <v>137</v>
+      </c>
+      <c r="E7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F7" t="s">
+        <v>127</v>
+      </c>
+      <c r="G7" t="n">
+        <v>23</v>
+      </c>
+      <c r="H7" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>22.2412570884934</v>
+      </c>
+      <c r="J7" t="n">
+        <v>208856.64</v>
+      </c>
+      <c r="K7" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-0.100000000000001</v>
+      </c>
+      <c r="N7" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="O7" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.188741721854305</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.2106135986733</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.0218718768189955</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.0800000000000001</v>
+      </c>
+      <c r="W7" t="n">
+        <v>5607.2349547541</v>
+      </c>
+      <c r="X7" t="n">
+        <v>5640.98602788571</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>33.7510731316142</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>6450.13328054237</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>8897.22287261538</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2447.08959207301</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>117.059891107078</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>146.551724137931</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>29.491833030853</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>138</v>
+      </c>
+      <c r="B8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" t="s">
+        <v>139</v>
+      </c>
+      <c r="E8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F8" t="s">
+        <v>127</v>
+      </c>
+      <c r="G8" t="n">
+        <v>22</v>
+      </c>
+      <c r="H8" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>20.6559283164331</v>
+      </c>
+      <c r="J8" t="n">
+        <v>141920.48</v>
+      </c>
+      <c r="K8" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="O8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.218683651804671</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.174636174636175</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0.0440474771684963</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3254.89592273684</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2725.23092121212</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-529.665001524721</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4096.57143870707</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>4983.73635589916</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>887.164917192091</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>70.7803992740472</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>92.5589836660617</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>21.7785843920145</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>140</v>
+      </c>
+      <c r="B9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" t="s">
+        <v>141</v>
+      </c>
+      <c r="E9" t="s">
+        <v>86</v>
+      </c>
+      <c r="F9" t="s">
+        <v>127</v>
+      </c>
+      <c r="G9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H9" t="n">
+        <v>67.9</v>
+      </c>
+      <c r="I9" t="n">
+        <v>22.4270048930319</v>
+      </c>
+      <c r="J9" t="n">
+        <v>229441.44</v>
+      </c>
+      <c r="K9" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N9" t="n">
+        <v>9.3</v>
+      </c>
+      <c r="O9" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.164893617021277</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.184300341296928</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.0194067242756517</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="W9"/>
+      <c r="X9"/>
+      <c r="Y9"/>
+      <c r="Z9"/>
+      <c r="AA9"/>
+      <c r="AB9"/>
+      <c r="AC9" t="n">
+        <v>106.624319419238</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>136.116152450091</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>29.491833030853</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>142</v>
+      </c>
+      <c r="B10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10" t="s">
+        <v>143</v>
+      </c>
+      <c r="E10" t="s">
+        <v>85</v>
+      </c>
+      <c r="F10" t="s">
+        <v>127</v>
+      </c>
+      <c r="G10" t="n">
+        <v>22</v>
+      </c>
+      <c r="H10" t="n">
+        <v>74.1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>22.1266684573469</v>
+      </c>
+      <c r="J10" t="n">
+        <v>231479.16</v>
+      </c>
+      <c r="K10" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="L10" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N10" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="O10" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.399999999999999</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.328385899814471</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.311151079136691</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-0.0172348206777806</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W10" t="n">
+        <v>5040.41702254546</v>
+      </c>
+      <c r="X10" t="n">
+        <v>5464.66452173913</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>424.247499193674</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5586.44431808</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>6884.1318384</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1297.68752032</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>99.8185117967332</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>127.041742286751</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>27.2232304900181</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>144</v>
+      </c>
+      <c r="B11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D11" t="s">
+        <v>145</v>
+      </c>
+      <c r="E11" t="s">
+        <v>86</v>
+      </c>
+      <c r="F11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G11" t="n">
+        <v>26</v>
+      </c>
+      <c r="H11" t="n">
+        <v>75</v>
+      </c>
+      <c r="I11" t="n">
+        <v>24.2122933841463</v>
+      </c>
+      <c r="J11" t="n">
+        <v>188532.28</v>
+      </c>
+      <c r="K11" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N11" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="O11" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.599999999999998</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.463414634146341</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.45703125</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.00638338414634149</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="W11" t="n">
+        <v>4189.93667986885</v>
+      </c>
+      <c r="X11" t="n">
+        <v>5345.18668586667</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1155.25000599781</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3518.95961516418</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>5424.57024784</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1905.61063267582</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>79.4010889292196</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>119.328493647913</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>39.9274047186933</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>146</v>
+      </c>
+      <c r="B12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" t="s">
+        <v>147</v>
+      </c>
+      <c r="E12" t="s">
+        <v>86</v>
+      </c>
+      <c r="F12" t="s">
+        <v>127</v>
+      </c>
+      <c r="G12" t="n">
+        <v>19</v>
+      </c>
+      <c r="H12" t="n">
+        <v>73</v>
+      </c>
+      <c r="I12" t="n">
+        <v>22.0384011651961</v>
+      </c>
+      <c r="J12" t="n">
+        <v>267915.11</v>
+      </c>
+      <c r="K12" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N12" t="n">
+        <v>9</v>
+      </c>
+      <c r="O12" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.147058823529412</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.176661264181524</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.0296024406521117</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="W12" t="n">
+        <v>5513.82293333333</v>
+      </c>
+      <c r="X12" t="n">
+        <v>5536.79625687273</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>22.9733235393933</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>8521.179672</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>9092.60773685106</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>571.428064851063</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>139.292196007259</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>178.312159709619</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>39.0199637023594</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>148</v>
+      </c>
+      <c r="B13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D13" t="s">
+        <v>149</v>
+      </c>
+      <c r="E13" t="s">
+        <v>87</v>
+      </c>
+      <c r="F13" t="s">
+        <v>127</v>
+      </c>
+      <c r="G13" t="n">
+        <v>20</v>
+      </c>
+      <c r="H13" t="n">
+        <v>78.4</v>
+      </c>
+      <c r="I13" t="n">
+        <v>23.93089344134</v>
+      </c>
+      <c r="J13" t="n">
+        <v>281749.13</v>
+      </c>
+      <c r="K13" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="L13" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.09999999999999</v>
+      </c>
+      <c r="N13" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.271356783919598</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.318770226537217</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.0474134426176189</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3851.4219404878</v>
+      </c>
+      <c r="X13" t="n">
+        <v>4778.24737307317</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>926.825432585368</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>5194.18641137778</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>5840.27335393939</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>646.086942561617</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>115.698729582577</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>147.459165154265</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>31.7604355716879</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>150</v>
+      </c>
+      <c r="B14" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" t="s">
+        <v>84</v>
+      </c>
+      <c r="D14" t="s">
+        <v>151</v>
+      </c>
+      <c r="E14" t="s">
+        <v>87</v>
+      </c>
+      <c r="F14" t="s">
+        <v>127</v>
+      </c>
+      <c r="G14" t="n">
+        <v>20</v>
+      </c>
+      <c r="H14" t="n">
+        <v>77</v>
+      </c>
+      <c r="I14" t="n">
+        <v>26.6435986134191</v>
+      </c>
+      <c r="J14" t="n">
+        <v>253228.17</v>
+      </c>
+      <c r="K14" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="L14" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N14" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="O14" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.362132352941176</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.368606701940035</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.00647434899885879</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="W14" t="n">
+        <v>6632.385552</v>
+      </c>
+      <c r="X14" t="n">
+        <v>6704.83684741818</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>72.4512954181819</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>7307.80120371428</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>6703.96993772308</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-603.831265991207</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>111.161524500907</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>161.070780399274</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>49.9092558983666</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>152</v>
+      </c>
+      <c r="B15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" t="s">
+        <v>153</v>
+      </c>
+      <c r="E15" t="s">
+        <v>87</v>
+      </c>
+      <c r="F15" t="s">
+        <v>127</v>
+      </c>
+      <c r="G15" t="n">
+        <v>21</v>
+      </c>
+      <c r="H15" t="n">
+        <v>91.47</v>
+      </c>
+      <c r="I15" t="n">
+        <v>25.8799230446976</v>
+      </c>
+      <c r="J15" t="n">
+        <v>203512.41</v>
+      </c>
+      <c r="K15" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="L15" t="n">
+        <v>65.6</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.09999999999999</v>
+      </c>
+      <c r="N15" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="O15" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.3984</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.342987804878049</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0.0554121951219512</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="W15" t="n">
+        <v>4835.6382008</v>
+      </c>
+      <c r="X15" t="n">
+        <v>4939.05335733333</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>103.415156533334</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>6220.85870474418</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>6454.55668156522</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>233.697976821034</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>97.5499092558984</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>141.107078039927</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>43.557168784029</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>154</v>
+      </c>
+      <c r="B16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D16" t="s">
+        <v>155</v>
+      </c>
+      <c r="E16" t="s">
+        <v>87</v>
+      </c>
+      <c r="F16" t="s">
+        <v>127</v>
+      </c>
+      <c r="G16" t="n">
+        <v>26</v>
+      </c>
+      <c r="H16" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="I16" t="n">
+        <v>22.5858290778869</v>
+      </c>
+      <c r="J16" t="n">
+        <v>195272.22</v>
+      </c>
+      <c r="K16" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="M16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N16" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="O16" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.227953410981697</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.233024691358025</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.00507128037632754</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2889.994398</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3520.173248</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>630.178849999999</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3677.1841585036</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>4841.109431</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1163.9252724964</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>97.5499092558984</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>131.125226860254</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>33.5753176043557</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>156</v>
+      </c>
+      <c r="B17" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" t="s">
+        <v>84</v>
+      </c>
+      <c r="D17" t="s">
+        <v>157</v>
+      </c>
+      <c r="E17" t="s">
+        <v>85</v>
+      </c>
+      <c r="F17" t="s">
+        <v>127</v>
+      </c>
+      <c r="G17" t="n">
+        <v>20</v>
+      </c>
+      <c r="H17" t="n">
+        <v>85.4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>27.8857142887719</v>
+      </c>
+      <c r="J17" t="n">
+        <v>280124.76</v>
+      </c>
+      <c r="K17" t="n">
+        <v>57</v>
+      </c>
+      <c r="L17" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N17" t="n">
+        <v>25</v>
+      </c>
+      <c r="O17" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.399999999999999</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.43859649122807</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.411669367909238</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0.026927123318832</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3881.88384492308</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3720.77560345946</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-161.108241463617</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4839.95057676191</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>5416.72341538461</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>576.772838622709</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>139.292196007259</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>179.219600725953</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>39.9274047186933</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>158</v>
+      </c>
+      <c r="B18" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" t="s">
+        <v>159</v>
+      </c>
+      <c r="E18" t="s">
+        <v>85</v>
+      </c>
+      <c r="F18" t="s">
+        <v>127</v>
+      </c>
+      <c r="G18" t="n">
+        <v>22</v>
+      </c>
+      <c r="H18" t="n">
+        <v>68.9</v>
+      </c>
+      <c r="I18" t="n">
+        <v>23.2896160065524</v>
+      </c>
+      <c r="J18" t="n">
+        <v>158570.78</v>
+      </c>
+      <c r="K18" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.799999999999997</v>
+      </c>
+      <c r="N18" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="O18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.255238095238095</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.215759849906191</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-0.0394782453319039</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="W18" t="n">
+        <v>4327.03944306383</v>
+      </c>
+      <c r="X18" t="n">
+        <v>4840.97618635294</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>513.936743289111</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5292.92958083168</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>5152.84480026891</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-140.084780562775</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>74.8638838475499</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>117.059891107078</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>42.1960072595281</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>160</v>
+      </c>
+      <c r="B19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" t="s">
+        <v>161</v>
+      </c>
+      <c r="E19" t="s">
+        <v>90</v>
+      </c>
+      <c r="F19" t="s">
+        <v>127</v>
+      </c>
+      <c r="G19" t="n">
+        <v>57</v>
+      </c>
+      <c r="H19" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>31.4440480908971</v>
+      </c>
+      <c r="J19" t="n">
+        <v>148013.636363636</v>
+      </c>
+      <c r="K19" t="n">
+        <v>57</v>
+      </c>
+      <c r="L19" t="n">
+        <v>57.7727272727273</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.772727272727273</v>
+      </c>
+      <c r="N19" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="O19" t="n">
+        <v>36.36</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.960000000000001</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.621052631578947</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.629362706530291</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.00831007495134384</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="W19"/>
+      <c r="X19"/>
+      <c r="Y19"/>
+      <c r="Z19"/>
+      <c r="AA19"/>
+      <c r="AB19"/>
+      <c r="AC19"/>
+      <c r="AD19"/>
+      <c r="AE19"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>162</v>
+      </c>
+      <c r="B20" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" t="s">
+        <v>94</v>
+      </c>
+      <c r="D20" t="s">
+        <v>163</v>
+      </c>
+      <c r="E20" t="s">
+        <v>90</v>
+      </c>
+      <c r="F20" t="s">
+        <v>127</v>
+      </c>
+      <c r="G20" t="n">
+        <v>58</v>
+      </c>
+      <c r="H20" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>28.7962962962963</v>
+      </c>
+      <c r="J20" t="n">
+        <v>172510</v>
+      </c>
+      <c r="K20" t="n">
+        <v>58.9545454545455</v>
+      </c>
+      <c r="L20" t="n">
+        <v>61.1363636363636</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.18181818181818</v>
+      </c>
+      <c r="N20" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>29.18</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.530917501927525</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.477293680297398</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-0.0536238216301273</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W20"/>
+      <c r="X20"/>
+      <c r="Y20"/>
+      <c r="Z20"/>
+      <c r="AA20"/>
+      <c r="AB20"/>
+      <c r="AC20"/>
+      <c r="AD20"/>
+      <c r="AE20"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>164</v>
+      </c>
+      <c r="B21" t="s">
+        <v>91</v>
+      </c>
+      <c r="C21" t="s">
+        <v>94</v>
+      </c>
+      <c r="D21" t="s">
+        <v>165</v>
+      </c>
+      <c r="E21" t="s">
+        <v>90</v>
+      </c>
+      <c r="F21" t="s">
+        <v>127</v>
+      </c>
+      <c r="G21" t="n">
+        <v>63</v>
+      </c>
+      <c r="H21" t="n">
+        <v>99</v>
+      </c>
+      <c r="I21" t="n">
+        <v>28.6160249739854</v>
+      </c>
+      <c r="J21" t="n">
+        <v>191457.954545455</v>
+      </c>
+      <c r="K21" t="n">
+        <v>64.9090909090909</v>
+      </c>
+      <c r="L21" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.590909090909079</v>
+      </c>
+      <c r="N21" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="O21" t="n">
+        <v>29.54</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.140000000000001</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.452941176470588</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.450992366412214</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-0.00194881005837438</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="W21"/>
+      <c r="X21"/>
+      <c r="Y21"/>
+      <c r="Z21"/>
+      <c r="AA21"/>
+      <c r="AB21"/>
+      <c r="AC21"/>
+      <c r="AD21"/>
+      <c r="AE21"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>166</v>
+      </c>
+      <c r="B22" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" t="s">
+        <v>167</v>
+      </c>
+      <c r="E22" t="s">
+        <v>89</v>
+      </c>
+      <c r="F22" t="s">
+        <v>127</v>
+      </c>
+      <c r="G22" t="n">
+        <v>50</v>
+      </c>
+      <c r="H22" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="I22" t="n">
+        <v>28.8255311847636</v>
+      </c>
+      <c r="J22" t="n">
+        <v>193640.909090909</v>
+      </c>
+      <c r="K22" t="n">
+        <v>61.1818181818182</v>
+      </c>
+      <c r="L22" t="n">
+        <v>63.5909090909091</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2.40909090909092</v>
+      </c>
+      <c r="N22" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="O22" t="n">
+        <v>36.54</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.0399999999999991</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.596582466567608</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.574610436025733</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-0.0219720305418752</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="W22"/>
+      <c r="X22"/>
+      <c r="Y22"/>
+      <c r="Z22"/>
+      <c r="AA22"/>
+      <c r="AB22"/>
+      <c r="AC22"/>
+      <c r="AD22"/>
+      <c r="AE22"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>168</v>
+      </c>
+      <c r="B23" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" t="s">
+        <v>169</v>
+      </c>
+      <c r="E23" t="s">
+        <v>93</v>
+      </c>
+      <c r="F23" t="s">
+        <v>127</v>
+      </c>
+      <c r="G23" t="n">
+        <v>42</v>
+      </c>
+      <c r="H23" t="n">
+        <v>80.2406</v>
+      </c>
+      <c r="I23" t="n">
+        <v>27</v>
+      </c>
+      <c r="J23" t="n">
+        <v>299211.655523401</v>
+      </c>
+      <c r="K23" t="n">
+        <v>56.3362393519065</v>
+      </c>
+      <c r="L23" t="n">
+        <v>56.8351915522857</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.4989522003792</v>
+      </c>
+      <c r="N23" t="n">
+        <v>21.3642</v>
+      </c>
+      <c r="O23" t="n">
+        <v>21.4549</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.0906999999999982</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.379226591014493</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.377493229353551</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-0.00173336166094129</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="W23" t="n">
+        <v>6520</v>
+      </c>
+      <c r="X23" t="n">
+        <v>4805</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>-1715</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>6960</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>4539</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>-2421</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>107.184004499642</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>117.389844961944</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>10.2058404623019</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>170</v>
+      </c>
+      <c r="B24" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" t="s">
+        <v>92</v>
+      </c>
+      <c r="D24" t="s">
+        <v>171</v>
+      </c>
+      <c r="E24" t="s">
+        <v>93</v>
+      </c>
+      <c r="F24" t="s">
+        <v>127</v>
+      </c>
+      <c r="G24" t="n">
+        <v>55</v>
+      </c>
+      <c r="H24" t="n">
+        <v>100.1987</v>
+      </c>
+      <c r="I24" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>239630.866090301</v>
+      </c>
+      <c r="K24" t="n">
+        <v>60.6000127006015</v>
+      </c>
+      <c r="L24" t="n">
+        <v>61.5071985194727</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.907185818871255</v>
+      </c>
+      <c r="N24" t="n">
+        <v>39.8708</v>
+      </c>
+      <c r="O24" t="n">
+        <v>35.6524</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-4.2184</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.657933855508982</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.579645974100295</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.0782878814086868</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="W24" t="n">
+        <v>4378</v>
+      </c>
+      <c r="X24" t="n">
+        <v>4655</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>277</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3990</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3521</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>-469</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>66.3606426504341</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>76.8386388583974</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>10.4779962079633</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>172</v>
+      </c>
+      <c r="B25" t="s">
+        <v>91</v>
+      </c>
+      <c r="C25" t="s">
+        <v>92</v>
+      </c>
+      <c r="D25" t="s">
+        <v>173</v>
+      </c>
+      <c r="E25" t="s">
+        <v>86</v>
+      </c>
+      <c r="F25" t="s">
+        <v>127</v>
+      </c>
+      <c r="G25" t="n">
+        <v>56</v>
+      </c>
+      <c r="H25" t="n">
+        <v>104.4624</v>
+      </c>
+      <c r="I25" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>323531.946548612</v>
+      </c>
+      <c r="K25" t="n">
+        <v>62.9586958296668</v>
+      </c>
+      <c r="L25" t="n">
+        <v>66.2245647776034</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.2658689479366</v>
+      </c>
+      <c r="N25" t="n">
+        <v>36.4689</v>
+      </c>
+      <c r="O25" t="n">
+        <v>35.7885</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.680399999999999</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.579251198256484</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.540411252534246</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.0388399457222375</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="W25"/>
+      <c r="X25"/>
+      <c r="Y25"/>
+      <c r="Z25"/>
+      <c r="AA25"/>
+      <c r="AB25"/>
+      <c r="AC25" t="n">
+        <v>130.135805717085</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>132.675926009925</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2.54012029283962</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>174</v>
+      </c>
+      <c r="B26" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" t="s">
+        <v>92</v>
+      </c>
+      <c r="D26" t="s">
+        <v>175</v>
+      </c>
+      <c r="E26" t="s">
+        <v>86</v>
+      </c>
+      <c r="F26" t="s">
+        <v>127</v>
+      </c>
+      <c r="G26" t="n">
+        <v>53</v>
+      </c>
+      <c r="H26" t="n">
+        <v>102.0584</v>
+      </c>
+      <c r="I26" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="J26" t="n">
+        <v>223120.991372663</v>
+      </c>
+      <c r="K26" t="n">
+        <v>69.9440266349756</v>
+      </c>
+      <c r="L26" t="n">
+        <v>71.3048053632826</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.36077872830693</v>
+      </c>
+      <c r="N26" t="n">
+        <v>24.6301</v>
+      </c>
+      <c r="O26" t="n">
+        <v>26.3084</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.6783</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.352140149559014</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.368956900814249</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.0168167512552351</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="W26" t="n">
+        <v>6872</v>
+      </c>
+      <c r="X26" t="n">
+        <v>7849</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>977</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>5188</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>4945</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>-243</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>153.087606934528</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>158.213206811151</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>5.12559987662272</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>176</v>
+      </c>
+      <c r="B27" t="s">
+        <v>91</v>
+      </c>
+      <c r="C27" t="s">
+        <v>92</v>
+      </c>
+      <c r="D27" t="s">
+        <v>177</v>
+      </c>
+      <c r="E27" t="s">
+        <v>93</v>
+      </c>
+      <c r="F27" t="s">
+        <v>127</v>
+      </c>
+      <c r="G27" t="n">
+        <v>64</v>
+      </c>
+      <c r="H27" t="n">
+        <v>83.325</v>
+      </c>
+      <c r="I27" t="n">
+        <v>26</v>
+      </c>
+      <c r="J27" t="n">
+        <v>203657.31962878</v>
+      </c>
+      <c r="K27" t="n">
+        <v>54.4765084232203</v>
+      </c>
+      <c r="L27" t="n">
+        <v>54.7940234598253</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.317515036604952</v>
+      </c>
+      <c r="N27" t="n">
+        <v>25.129</v>
+      </c>
+      <c r="O27" t="n">
+        <v>26.5352</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.4062</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.461281398667777</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.484271793245033</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.0229903945772562</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="W27" t="n">
+        <v>6547</v>
+      </c>
+      <c r="X27" t="n">
+        <v>5296</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>-1251</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>4244</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3652</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>-592</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>63.775163066651</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>81.6467236984152</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>17.8715606317642</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>178</v>
+      </c>
+      <c r="B28" t="s">
+        <v>91</v>
+      </c>
+      <c r="C28" t="s">
+        <v>92</v>
+      </c>
+      <c r="D28" t="s">
+        <v>179</v>
+      </c>
+      <c r="E28" t="s">
+        <v>93</v>
+      </c>
+      <c r="F28" t="s">
+        <v>127</v>
+      </c>
+      <c r="G28" t="n">
+        <v>69</v>
+      </c>
+      <c r="H28" t="n">
+        <v>106.3675</v>
+      </c>
+      <c r="I28" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>242107.936968729</v>
+      </c>
+      <c r="K28" t="n">
+        <v>61.4164799375856</v>
+      </c>
+      <c r="L28" t="n">
+        <v>62.2329471745698</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.816467236984153</v>
+      </c>
+      <c r="N28" t="n">
+        <v>39.7347</v>
+      </c>
+      <c r="O28" t="n">
+        <v>40.5966</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.861900000000006</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.646971302171344</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.652332917580175</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.00536161540883084</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="W28" t="n">
+        <v>3853</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3965</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>112</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3164</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3196</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>112.264245085321</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>81.6467236984152</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>-30.6175213869056</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>180</v>
+      </c>
+      <c r="B29" t="s">
+        <v>91</v>
+      </c>
+      <c r="C29" t="s">
+        <v>92</v>
+      </c>
+      <c r="D29" t="s">
+        <v>181</v>
+      </c>
+      <c r="E29" t="s">
+        <v>86</v>
+      </c>
+      <c r="F29" t="s">
+        <v>127</v>
+      </c>
+      <c r="G29" t="n">
+        <v>60</v>
+      </c>
+      <c r="H29" t="n">
+        <v>68.7647</v>
+      </c>
+      <c r="I29" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>86021.1737170125</v>
+      </c>
+      <c r="K29" t="n">
+        <v>44.3613865428056</v>
+      </c>
+      <c r="L29" t="n">
+        <v>44.2253086699749</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-0.136077872830697</v>
+      </c>
+      <c r="N29" t="n">
+        <v>20.7292</v>
+      </c>
+      <c r="O29" t="n">
+        <v>21.4096</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.680400000000002</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.467280254642127</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.484102895917949</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.0168226412758221</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="W29" t="n">
+        <v>4195</v>
+      </c>
+      <c r="X29" t="n">
+        <v>4432</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>237</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3067</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>3335</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>268</v>
+      </c>
+      <c r="AC29"/>
+      <c r="AD29"/>
+      <c r="AE29"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>182</v>
+      </c>
+      <c r="B30" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" t="s">
+        <v>92</v>
+      </c>
+      <c r="D30" t="s">
+        <v>183</v>
+      </c>
+      <c r="E30" t="s">
+        <v>86</v>
+      </c>
+      <c r="F30" t="s">
+        <v>127</v>
+      </c>
+      <c r="G30" t="n">
+        <v>63</v>
+      </c>
+      <c r="H30" t="n">
+        <v>91.8979</v>
+      </c>
+      <c r="I30" t="n">
+        <v>31</v>
+      </c>
+      <c r="J30" t="n">
+        <v>244238.916457258</v>
+      </c>
+      <c r="K30" t="n">
+        <v>58.1959702805926</v>
+      </c>
+      <c r="L30" t="n">
+        <v>59.7381861726737</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.54221589208117</v>
+      </c>
+      <c r="N30" t="n">
+        <v>31.3433</v>
+      </c>
+      <c r="O30" t="n">
+        <v>29.3021</v>
+      </c>
+      <c r="P30" t="n">
+        <v>-2.0412</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.538581964505066</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.490508699331815</v>
+      </c>
+      <c r="S30" t="n">
+        <v>-0.0480732651732514</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="W30" t="n">
+        <v>6457</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3172</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>-3285</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>5663</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>3658</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>-2005</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>66.3606426504341</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>102.058404623019</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>35.6977619725848</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>184</v>
+      </c>
+      <c r="B31" t="s">
+        <v>91</v>
+      </c>
+      <c r="C31" t="s">
+        <v>92</v>
+      </c>
+      <c r="D31" t="s">
+        <v>185</v>
+      </c>
+      <c r="E31" t="s">
+        <v>86</v>
+      </c>
+      <c r="F31" t="s">
+        <v>127</v>
+      </c>
+      <c r="G31" t="n">
+        <v>60</v>
+      </c>
+      <c r="H31" t="n">
+        <v>80.6035</v>
+      </c>
+      <c r="I31" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>119016.42913518</v>
+      </c>
+      <c r="K31" t="n">
+        <v>48.4437227277263</v>
+      </c>
+      <c r="L31" t="n">
+        <v>48.3076448548956</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-0.13607787283069</v>
+      </c>
+      <c r="N31" t="n">
+        <v>28.5764</v>
+      </c>
+      <c r="O31" t="n">
+        <v>28.6217</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.045300000000001</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.589888604569288</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.592488002384977</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.00259939781568819</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W31" t="n">
+        <v>3051</v>
+      </c>
+      <c r="X31" t="n">
+        <v>2336</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>-715</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3300</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3710</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>410</v>
+      </c>
+      <c r="AC31"/>
+      <c r="AD31"/>
+      <c r="AE31"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>186</v>
+      </c>
+      <c r="B32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C32" t="s">
+        <v>92</v>
+      </c>
+      <c r="D32" t="s">
+        <v>187</v>
+      </c>
+      <c r="E32" t="s">
+        <v>93</v>
+      </c>
+      <c r="F32" t="s">
+        <v>127</v>
+      </c>
+      <c r="G32" t="n">
+        <v>50</v>
+      </c>
+      <c r="H32" t="n">
+        <v>89.9928</v>
+      </c>
+      <c r="I32" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>269210.566900418</v>
+      </c>
+      <c r="K32" t="n">
+        <v>52.9342925311392</v>
+      </c>
+      <c r="L32" t="n">
+        <v>53.8414783500104</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.907185818871284</v>
+      </c>
+      <c r="N32" t="n">
+        <v>33.1123</v>
+      </c>
+      <c r="O32" t="n">
+        <v>33.203</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.0907000000000053</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.625535893967438</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.616680689637742</v>
+      </c>
+      <c r="S32" t="n">
+        <v>-0.00885520432969567</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V32" t="n">
+        <v>-0.0499999999999998</v>
+      </c>
+      <c r="W32" t="n">
+        <v>4784</v>
+      </c>
+      <c r="X32" t="n">
+        <v>4800</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3893</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>4879</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>986</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>81.6467236984152</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>112.264245085321</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>30.6175213869056</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>188</v>
+      </c>
+      <c r="B33" t="s">
+        <v>91</v>
+      </c>
+      <c r="C33" t="s">
+        <v>92</v>
+      </c>
+      <c r="D33" t="s">
+        <v>189</v>
+      </c>
+      <c r="E33" t="s">
+        <v>93</v>
+      </c>
+      <c r="F33" t="s">
+        <v>127</v>
+      </c>
+      <c r="G33" t="n">
+        <v>63</v>
+      </c>
+      <c r="H33" t="n">
+        <v>87.9063</v>
+      </c>
+      <c r="I33" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="J33" t="n">
+        <v>223190.391087806</v>
+      </c>
+      <c r="K33" t="n">
+        <v>62.5504622111747</v>
+      </c>
+      <c r="L33" t="n">
+        <v>64.9545046311836</v>
+      </c>
+      <c r="M33" t="n">
+        <v>2.40404242000888</v>
+      </c>
+      <c r="N33" t="n">
+        <v>20.1395</v>
+      </c>
+      <c r="O33" t="n">
+        <v>19.4138</v>
+      </c>
+      <c r="P33" t="n">
+        <v>-0.725700000000003</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.321972041261784</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.298883042988827</v>
+      </c>
+      <c r="S33" t="n">
+        <v>-0.0230889982729571</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="W33" t="n">
+        <v>7122</v>
+      </c>
+      <c r="X33" t="n">
+        <v>5243</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>-1879</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>5944</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>6162</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>218</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>81.6467236984152</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>112.264245085321</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>30.6175213869056</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="15.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="250.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>198</v>
+      </c>
+      <c r="B5" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>200</v>
+      </c>
+      <c r="B6" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>202</v>
+      </c>
+      <c r="B7" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>204</v>
+      </c>
+      <c r="B8" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>206</v>
+      </c>
+      <c r="B9" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>208</v>
+      </c>
+      <c r="B10" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>210</v>
+      </c>
+      <c r="B11" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>212</v>
+      </c>
+      <c r="B12" t="s">
+        <v>213</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="3.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="11.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="11.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="11.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="11.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C2" t="n">
+        <v>211904.046228677</v>
+      </c>
+      <c r="D2" t="n">
+        <v>63961.6607283764</v>
+      </c>
+      <c r="E2" t="n">
+        <v>16514.8297864514</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.988399773207149</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.770720789789444</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C3" t="n">
+        <v>217658.102941176</v>
+      </c>
+      <c r="D3" t="n">
+        <v>42922.5053682504</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10410.236667614</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.505766494479598</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.770720789789444</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="12.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="3.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="11.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="11.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="11.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="11.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="11.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="11.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5.7029557765547</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0000326648431024457</v>
+      </c>
+      <c r="F2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.73294117647059</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.71705104695603</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.74883130598515</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.120615249885259</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.5719266262061</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0004351155884287</v>
+      </c>
+      <c r="F3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.18017345392857</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.626529329608829</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.7338175782483</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.308889212998157</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B4" t="s">
+        <v>230</v>
+      </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D4" t="n">
-        <v>2.74542435658255</v>
+        <v>2.85269264066161</v>
       </c>
       <c r="E4" t="n">
-        <v>0.015399032964439</v>
+        <v>0.00871961260673947</v>
       </c>
       <c r="F4" t="n">
-        <v>14.4882690796857</v>
+        <v>24.2944968768741</v>
       </c>
       <c r="G4" t="n">
-        <v>-1294.68526156664</v>
+        <v>1.55276772254202</v>
       </c>
       <c r="H4" t="n">
-        <v>286.436818157853</v>
+        <v>0.430073856013771</v>
       </c>
       <c r="I4" t="n">
-        <v>2302.93370497542</v>
+        <v>2.67546158907028</v>
+      </c>
+      <c r="J4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="12.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="3.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="11.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="11.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="11.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="11.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="11.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="11.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6.92343113446106</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0000034277271010321</v>
+      </c>
+      <c r="F2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.488235294117647</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.338741124656624</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.637729463578671</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.262958948746454</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5.27132264595624</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.00011816977551927</v>
+      </c>
+      <c r="F3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.204666666666667</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.121392245499539</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.287941087833794</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.628876363010418</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C4" t="n">
+        <v>32</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.5225347896415</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.00169792034521066</v>
+      </c>
+      <c r="F4" t="n">
+        <v>24.5884039413238</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.28356862745098</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.117632259791619</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.449504995110342</v>
       </c>
       <c r="J4"/>
     </row>
